--- a/Desafio 4 - Vale Refeição/Desafio 4 - Dados/BASE DIAS ÚTEIS POR SINDICATO.xlsx
+++ b/Desafio 4 - Vale Refeição/Desafio 4 - Dados/BASE DIAS ÚTEIS POR SINDICATO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Meu Drive\Cursos e Treinamentos\Cientista de Dados\Treinamento Python\I2A2\Desafios\Desafio 4 - Vale Refeição\Desafio 4 - Dados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{120D959F-2652-4021-A717-E4BCE3081F8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF82403A-999F-42F3-9D97-1DB5D441F68E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FEAC6BF2-C67E-44DA-A616-6A8EDEF16B11}"/>
   </bookViews>
@@ -30,8 +30,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
@@ -42,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>BASE DIAS UTEIS DE 15/04 a 15/05</t>
   </si>
@@ -63,6 +61,9 @@
   </si>
   <si>
     <t xml:space="preserve">DIAS UTEIS </t>
+  </si>
+  <si>
+    <t>Feriados</t>
   </si>
 </sst>
 </file>
@@ -485,21 +486,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12D4A894-BE5F-4920-9800-4641A6D62D80}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="44" customWidth="1"/>
     <col min="2" max="2" width="17.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15">
+    <row r="1" spans="1:4" ht="15">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="5"/>
-    </row>
-    <row r="2" spans="1:2">
+      <c r="D1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="4" t="s">
         <v>5</v>
       </c>
@@ -507,7 +510,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="42.75" hidden="1">
+    <row r="3" spans="1:4" ht="42.75">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -515,7 +518,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="28.5" hidden="1">
+    <row r="4" spans="1:4" ht="28.5">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -523,7 +526,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="42.75">
+    <row r="5" spans="1:4" ht="42.75">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -531,7 +534,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="28.5" hidden="1">
+    <row r="6" spans="1:4" ht="28.5">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -539,17 +542,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:4">
       <c r="B7" s="3"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:B6" xr:uid="{12D4A894-BE5F-4920-9800-4641A6D62D80}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="SINDPD SP - SIND.TRAB.EM PROC DADOS E EMPR.EMPRESAS PROC DADOS ESTADO DE SP."/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A2:B6" xr:uid="{12D4A894-BE5F-4920-9800-4641A6D62D80}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:B1"/>
   </mergeCells>
